--- a/Intermodel comparison/grab7/Standing/Mean_SD_comparison/results/validation_results.xlsx
+++ b/Intermodel comparison/grab7/Standing/Mean_SD_comparison/results/validation_results.xlsx
@@ -8,13 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="Comparison_A_full" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Comparison_B_full" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Comparison_B1_full" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Summary_A_Peak" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Summary_A_Valley" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Summary_A_ROM" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Summary_B" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Comparison_C_full" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Summary_C" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Summary_B1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Comparison_B2_full" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary_B2" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,10 +456,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q181"/>
+  <dimension ref="A1:R181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
@@ -476,6 +476,7 @@
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -564,11 +565,16 @@
           <t>shapiro_p</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>zero_variance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -629,11 +635,14 @@
       <c r="Q2" s="2" t="n">
         <v>4.135612088831233e-06</v>
       </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -694,11 +703,14 @@
       <c r="Q3" s="2" t="n">
         <v>4.135612088444794e-06</v>
       </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -759,11 +771,14 @@
       <c r="Q4" s="2" t="n">
         <v>4.135612088812119e-06</v>
       </c>
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -824,11 +839,14 @@
       <c r="Q5" s="2" t="n">
         <v>4.135612088541419e-06</v>
       </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -889,11 +907,14 @@
       <c r="Q6" s="2" t="n">
         <v>0.0002751787013169948</v>
       </c>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -954,11 +975,14 @@
       <c r="Q7" s="2" t="n">
         <v>0.001497441315277268</v>
       </c>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1014,16 +1038,19 @@
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1079,16 +1106,19 @@
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1144,16 +1174,19 @@
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1214,11 +1247,14 @@
       <c r="Q11" s="2" t="n">
         <v>0.001497441315311478</v>
       </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1274,16 +1310,19 @@
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R12" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1344,11 +1383,14 @@
       <c r="Q13" s="2" t="n">
         <v>0.0002751787013147552</v>
       </c>
+      <c r="R13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1409,11 +1451,14 @@
       <c r="Q14" s="2" t="n">
         <v>0.0002751787013193635</v>
       </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1474,11 +1519,14 @@
       <c r="Q15" s="2" t="n">
         <v>4.135612088444849e-06</v>
       </c>
+      <c r="R15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1539,11 +1587,14 @@
       <c r="Q16" s="2" t="n">
         <v>4.135612088444849e-06</v>
       </c>
+      <c r="R16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1599,16 +1650,19 @@
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R17" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1664,16 +1718,19 @@
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R18" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1729,16 +1786,19 @@
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R19" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1799,11 +1859,14 @@
       <c r="Q20" s="2" t="n">
         <v>0.8382167274117611</v>
       </c>
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1864,11 +1927,14 @@
       <c r="Q21" s="2" t="n">
         <v>0.8585016631374679</v>
       </c>
+      <c r="R21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1929,11 +1995,14 @@
       <c r="Q22" s="2" t="n">
         <v>0.9302758967505163</v>
       </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1994,11 +2063,14 @@
       <c r="Q23" s="2" t="n">
         <v>0.699408373463996</v>
       </c>
+      <c r="R23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2059,11 +2131,14 @@
       <c r="Q24" s="2" t="n">
         <v>0.6651998297338304</v>
       </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2124,11 +2199,14 @@
       <c r="Q25" s="2" t="n">
         <v>0.62347829592471</v>
       </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2189,11 +2267,14 @@
       <c r="Q26" s="2" t="n">
         <v>0.6102722601506456</v>
       </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2254,11 +2335,14 @@
       <c r="Q27" s="2" t="n">
         <v>0.4334311985612253</v>
       </c>
+      <c r="R27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2319,11 +2403,14 @@
       <c r="Q28" s="2" t="n">
         <v>0.6642585038849866</v>
       </c>
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2384,11 +2471,14 @@
       <c r="Q29" s="2" t="n">
         <v>0.7819089424948584</v>
       </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2449,11 +2539,14 @@
       <c r="Q30" s="2" t="n">
         <v>0.4193829819568353</v>
       </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2514,11 +2607,14 @@
       <c r="Q31" s="2" t="n">
         <v>0.7749983152837765</v>
       </c>
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2579,11 +2675,14 @@
       <c r="Q32" s="2" t="n">
         <v>0.3799972545443137</v>
       </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2644,11 +2743,14 @@
       <c r="Q33" s="2" t="n">
         <v>0.1575526051052755</v>
       </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2709,11 +2811,14 @@
       <c r="Q34" s="2" t="n">
         <v>0.2778602255343585</v>
       </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2774,11 +2879,14 @@
       <c r="Q35" s="2" t="n">
         <v>0.7157571867897479</v>
       </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2839,11 +2947,14 @@
       <c r="Q36" s="2" t="n">
         <v>0.7388654969521693</v>
       </c>
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2904,11 +3015,14 @@
       <c r="Q37" s="2" t="n">
         <v>0.5995113025180017</v>
       </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2964,16 +3078,19 @@
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R38" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3029,16 +3146,19 @@
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q39" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R39" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3094,16 +3214,19 @@
         </is>
       </c>
       <c r="P40" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R40" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3159,16 +3282,19 @@
         </is>
       </c>
       <c r="P41" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q41" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R41" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3224,16 +3350,19 @@
         </is>
       </c>
       <c r="P42" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R42" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3289,16 +3418,19 @@
         </is>
       </c>
       <c r="P43" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q43" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R43" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3354,16 +3486,19 @@
         </is>
       </c>
       <c r="P44" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R44" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3419,16 +3554,19 @@
         </is>
       </c>
       <c r="P45" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q45" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R45" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3484,16 +3622,19 @@
         </is>
       </c>
       <c r="P46" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R46" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3549,16 +3690,19 @@
         </is>
       </c>
       <c r="P47" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q47" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R47" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3614,16 +3758,19 @@
         </is>
       </c>
       <c r="P48" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R48" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3679,16 +3826,19 @@
         </is>
       </c>
       <c r="P49" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q49" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R49" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3744,16 +3894,19 @@
         </is>
       </c>
       <c r="P50" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R50" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3809,16 +3962,19 @@
         </is>
       </c>
       <c r="P51" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q51" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R51" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3874,16 +4030,19 @@
         </is>
       </c>
       <c r="P52" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R52" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3939,16 +4098,19 @@
         </is>
       </c>
       <c r="P53" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q53" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R53" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4004,16 +4166,19 @@
         </is>
       </c>
       <c r="P54" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R54" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4069,16 +4234,19 @@
         </is>
       </c>
       <c r="P55" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q55" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R55" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4134,16 +4302,19 @@
         </is>
       </c>
       <c r="P56" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R56" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4199,16 +4370,19 @@
         </is>
       </c>
       <c r="P57" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q57" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R57" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4264,16 +4438,19 @@
         </is>
       </c>
       <c r="P58" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q58" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R58" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4329,16 +4506,19 @@
         </is>
       </c>
       <c r="P59" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q59" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R59" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4394,16 +4574,19 @@
         </is>
       </c>
       <c r="P60" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q60" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R60" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4459,16 +4642,19 @@
         </is>
       </c>
       <c r="P61" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q61" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R61" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4524,16 +4710,19 @@
         </is>
       </c>
       <c r="P62" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q62" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R62" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4589,16 +4778,19 @@
         </is>
       </c>
       <c r="P63" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q63" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R63" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4654,16 +4846,19 @@
         </is>
       </c>
       <c r="P64" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R64" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4719,16 +4914,19 @@
         </is>
       </c>
       <c r="P65" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q65" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R65" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4784,16 +4982,19 @@
         </is>
       </c>
       <c r="P66" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R66" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4849,16 +5050,19 @@
         </is>
       </c>
       <c r="P67" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q67" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R67" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4914,16 +5118,19 @@
         </is>
       </c>
       <c r="P68" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q68" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R68" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4979,16 +5186,19 @@
         </is>
       </c>
       <c r="P69" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q69" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R69" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5044,16 +5254,19 @@
         </is>
       </c>
       <c r="P70" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R70" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5109,16 +5322,19 @@
         </is>
       </c>
       <c r="P71" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q71" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R71" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5174,16 +5390,19 @@
         </is>
       </c>
       <c r="P72" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R72" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5239,16 +5458,19 @@
         </is>
       </c>
       <c r="P73" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q73" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R73" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5304,16 +5526,19 @@
         </is>
       </c>
       <c r="P74" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R74" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5369,16 +5594,19 @@
         </is>
       </c>
       <c r="P75" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q75" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R75" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5434,16 +5662,19 @@
         </is>
       </c>
       <c r="P76" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R76" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5499,16 +5730,19 @@
         </is>
       </c>
       <c r="P77" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q77" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R77" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5564,16 +5798,19 @@
         </is>
       </c>
       <c r="P78" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R78" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5629,16 +5866,19 @@
         </is>
       </c>
       <c r="P79" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q79" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R79" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5694,16 +5934,19 @@
         </is>
       </c>
       <c r="P80" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R80" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5759,16 +6002,19 @@
         </is>
       </c>
       <c r="P81" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R81" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5824,16 +6070,19 @@
         </is>
       </c>
       <c r="P82" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R82" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5894,11 +6143,14 @@
       <c r="Q83" s="2" t="n">
         <v>0.3445563525280878</v>
       </c>
+      <c r="R83" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5959,11 +6211,14 @@
       <c r="Q84" s="2" t="n">
         <v>0.3321728966489961</v>
       </c>
+      <c r="R84" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6024,11 +6279,14 @@
       <c r="Q85" s="2" t="n">
         <v>0.29858937264157</v>
       </c>
+      <c r="R85" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6089,11 +6347,14 @@
       <c r="Q86" s="2" t="n">
         <v>0.5224424402280525</v>
       </c>
+      <c r="R86" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6154,11 +6415,14 @@
       <c r="Q87" s="2" t="n">
         <v>0.5178479550743772</v>
       </c>
+      <c r="R87" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6219,11 +6483,14 @@
       <c r="Q88" s="2" t="n">
         <v>0.4393039535687537</v>
       </c>
+      <c r="R88" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6284,11 +6551,14 @@
       <c r="Q89" s="2" t="n">
         <v>0.7898502814840732</v>
       </c>
+      <c r="R89" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6349,11 +6619,14 @@
       <c r="Q90" s="2" t="n">
         <v>0.8000152566346065</v>
       </c>
+      <c r="R90" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6414,11 +6687,14 @@
       <c r="Q91" s="2" t="n">
         <v>0.6884882599268742</v>
       </c>
+      <c r="R91" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6474,16 +6750,19 @@
         </is>
       </c>
       <c r="P92" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R92" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6539,16 +6818,19 @@
         </is>
       </c>
       <c r="P93" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R93" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6609,11 +6891,14 @@
       <c r="Q94" s="2" t="n">
         <v>0.0002751787013147533</v>
       </c>
+      <c r="R94" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6674,11 +6959,14 @@
       <c r="Q95" s="2" t="n">
         <v>0.0002751787013147552</v>
       </c>
+      <c r="R95" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6739,11 +7027,14 @@
       <c r="Q96" s="2" t="n">
         <v>0.001497441315269922</v>
       </c>
+      <c r="R96" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6804,11 +7095,14 @@
       <c r="Q97" s="2" t="n">
         <v>4.135612088511198e-06</v>
       </c>
+      <c r="R97" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6864,16 +7158,19 @@
         </is>
       </c>
       <c r="P98" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R98" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6929,16 +7226,19 @@
         </is>
       </c>
       <c r="P99" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R99" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6994,16 +7294,19 @@
         </is>
       </c>
       <c r="P100" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R100" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7064,11 +7367,14 @@
       <c r="Q101" s="2" t="n">
         <v>0.001497441315294336</v>
       </c>
+      <c r="R101" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7129,11 +7435,14 @@
       <c r="Q102" s="2" t="n">
         <v>0.0002751787013147533</v>
       </c>
+      <c r="R102" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7194,11 +7503,14 @@
       <c r="Q103" s="2" t="n">
         <v>4.135612088831233e-06</v>
       </c>
+      <c r="R103" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7259,11 +7571,14 @@
       <c r="Q104" s="2" t="n">
         <v>4.135612088496812e-06</v>
       </c>
+      <c r="R104" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7324,11 +7639,14 @@
       <c r="Q105" s="2" t="n">
         <v>4.135612088444794e-06</v>
       </c>
+      <c r="R105" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7384,16 +7702,19 @@
         </is>
       </c>
       <c r="P106" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R106" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7449,16 +7770,19 @@
         </is>
       </c>
       <c r="P107" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R107" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7514,16 +7838,19 @@
         </is>
       </c>
       <c r="P108" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R108" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7579,16 +7906,19 @@
         </is>
       </c>
       <c r="P109" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R109" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7649,11 +7979,14 @@
       <c r="Q110" s="2" t="n">
         <v>0.1267872954571129</v>
       </c>
+      <c r="R110" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7714,11 +8047,14 @@
       <c r="Q111" s="2" t="n">
         <v>0.2152546027435818</v>
       </c>
+      <c r="R111" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7779,11 +8115,14 @@
       <c r="Q112" s="2" t="n">
         <v>0.189039779406352</v>
       </c>
+      <c r="R112" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7844,11 +8183,14 @@
       <c r="Q113" s="2" t="n">
         <v>0.3961962551523391</v>
       </c>
+      <c r="R113" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7909,11 +8251,14 @@
       <c r="Q114" s="2" t="n">
         <v>0.4869200650395129</v>
       </c>
+      <c r="R114" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7974,11 +8319,14 @@
       <c r="Q115" s="2" t="n">
         <v>0.3248245391094484</v>
       </c>
+      <c r="R115" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8039,11 +8387,14 @@
       <c r="Q116" s="2" t="n">
         <v>0.599134672736681</v>
       </c>
+      <c r="R116" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8104,11 +8455,14 @@
       <c r="Q117" s="2" t="n">
         <v>0.6213737416358016</v>
       </c>
+      <c r="R117" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8169,11 +8523,14 @@
       <c r="Q118" s="2" t="n">
         <v>0.7186307317541788</v>
       </c>
+      <c r="R118" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8234,11 +8591,14 @@
       <c r="Q119" s="2" t="n">
         <v>0.2191790192658555</v>
       </c>
+      <c r="R119" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8299,11 +8659,14 @@
       <c r="Q120" s="2" t="n">
         <v>0.01257856561058879</v>
       </c>
+      <c r="R120" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8364,11 +8727,14 @@
       <c r="Q121" s="2" t="n">
         <v>0.005441471889439938</v>
       </c>
+      <c r="R121" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8429,11 +8795,14 @@
       <c r="Q122" s="2" t="n">
         <v>0.02490262175714809</v>
       </c>
+      <c r="R122" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8494,11 +8863,14 @@
       <c r="Q123" s="2" t="n">
         <v>0.03351461328034879</v>
       </c>
+      <c r="R123" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8559,11 +8931,14 @@
       <c r="Q124" s="2" t="n">
         <v>0.02685813888167764</v>
       </c>
+      <c r="R124" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8624,11 +8999,14 @@
       <c r="Q125" s="2" t="n">
         <v>0.5683843211510499</v>
       </c>
+      <c r="R125" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8689,11 +9067,14 @@
       <c r="Q126" s="2" t="n">
         <v>0.4423822021495249</v>
       </c>
+      <c r="R126" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8754,11 +9135,14 @@
       <c r="Q127" s="2" t="n">
         <v>0.591033931459237</v>
       </c>
+      <c r="R127" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8814,16 +9198,19 @@
         </is>
       </c>
       <c r="P128" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R128" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8879,16 +9266,19 @@
         </is>
       </c>
       <c r="P129" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R129" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8944,16 +9334,19 @@
         </is>
       </c>
       <c r="P130" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q130" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R130" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9009,16 +9402,19 @@
         </is>
       </c>
       <c r="P131" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q131" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R131" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9074,16 +9470,19 @@
         </is>
       </c>
       <c r="P132" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q132" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R132" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9139,16 +9538,19 @@
         </is>
       </c>
       <c r="P133" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q133" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R133" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9204,16 +9606,19 @@
         </is>
       </c>
       <c r="P134" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q134" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R134" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9269,16 +9674,19 @@
         </is>
       </c>
       <c r="P135" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q135" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R135" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9334,16 +9742,19 @@
         </is>
       </c>
       <c r="P136" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q136" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R136" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9399,16 +9810,19 @@
         </is>
       </c>
       <c r="P137" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q137" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R137" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9464,16 +9878,19 @@
         </is>
       </c>
       <c r="P138" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q138" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R138" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9529,16 +9946,19 @@
         </is>
       </c>
       <c r="P139" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q139" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R139" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9594,16 +10014,19 @@
         </is>
       </c>
       <c r="P140" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q140" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R140" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9659,16 +10082,19 @@
         </is>
       </c>
       <c r="P141" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q141" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R141" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9724,16 +10150,19 @@
         </is>
       </c>
       <c r="P142" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q142" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R142" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9789,16 +10218,19 @@
         </is>
       </c>
       <c r="P143" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q143" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R143" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9854,16 +10286,19 @@
         </is>
       </c>
       <c r="P144" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q144" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R144" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9919,16 +10354,19 @@
         </is>
       </c>
       <c r="P145" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q145" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R145" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9984,16 +10422,19 @@
         </is>
       </c>
       <c r="P146" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q146" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R146" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -10049,16 +10490,19 @@
         </is>
       </c>
       <c r="P147" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q147" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R147" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10114,16 +10558,19 @@
         </is>
       </c>
       <c r="P148" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q148" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R148" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10179,16 +10626,19 @@
         </is>
       </c>
       <c r="P149" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q149" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R149" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10244,16 +10694,19 @@
         </is>
       </c>
       <c r="P150" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q150" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R150" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10309,16 +10762,19 @@
         </is>
       </c>
       <c r="P151" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q151" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R151" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10374,16 +10830,19 @@
         </is>
       </c>
       <c r="P152" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q152" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R152" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10439,16 +10898,19 @@
         </is>
       </c>
       <c r="P153" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q153" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R153" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10504,16 +10966,19 @@
         </is>
       </c>
       <c r="P154" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q154" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R154" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10569,16 +11034,19 @@
         </is>
       </c>
       <c r="P155" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q155" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R155" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10634,16 +11102,19 @@
         </is>
       </c>
       <c r="P156" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q156" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R156" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10699,16 +11170,19 @@
         </is>
       </c>
       <c r="P157" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q157" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R157" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10764,16 +11238,19 @@
         </is>
       </c>
       <c r="P158" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q158" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R158" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10829,16 +11306,19 @@
         </is>
       </c>
       <c r="P159" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q159" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R159" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10894,16 +11374,19 @@
         </is>
       </c>
       <c r="P160" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q160" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R160" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10959,16 +11442,19 @@
         </is>
       </c>
       <c r="P161" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q161" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R161" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11024,16 +11510,19 @@
         </is>
       </c>
       <c r="P162" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q162" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R162" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11089,16 +11578,19 @@
         </is>
       </c>
       <c r="P163" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q163" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R163" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11154,16 +11646,19 @@
         </is>
       </c>
       <c r="P164" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q164" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R164" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11219,16 +11714,19 @@
         </is>
       </c>
       <c r="P165" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q165" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R165" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11284,16 +11782,19 @@
         </is>
       </c>
       <c r="P166" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q166" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R166" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11349,16 +11850,19 @@
         </is>
       </c>
       <c r="P167" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q167" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R167" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11414,16 +11918,19 @@
         </is>
       </c>
       <c r="P168" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q168" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R168" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11479,16 +11986,19 @@
         </is>
       </c>
       <c r="P169" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q169" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R169" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11544,16 +12054,19 @@
         </is>
       </c>
       <c r="P170" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q170" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R170" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11609,16 +12122,19 @@
         </is>
       </c>
       <c r="P171" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q171" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R171" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11674,16 +12190,19 @@
         </is>
       </c>
       <c r="P172" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="Q172" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R172" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11744,11 +12263,14 @@
       <c r="Q173" s="2" t="n">
         <v>0.89563004923182</v>
       </c>
+      <c r="R173" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11809,11 +12331,14 @@
       <c r="Q174" s="2" t="n">
         <v>0.9077749306097378</v>
       </c>
+      <c r="R174" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11874,11 +12399,14 @@
       <c r="Q175" s="2" t="n">
         <v>0.8890876422040619</v>
       </c>
+      <c r="R175" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11939,11 +12467,14 @@
       <c r="Q176" s="2" t="n">
         <v>0.3704971963095017</v>
       </c>
+      <c r="R176" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -12004,11 +12535,14 @@
       <c r="Q177" s="2" t="n">
         <v>0.3760770235959953</v>
       </c>
+      <c r="R177" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -12069,11 +12603,14 @@
       <c r="Q178" s="2" t="n">
         <v>0.376893456173956</v>
       </c>
+      <c r="R178" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12134,11 +12671,14 @@
       <c r="Q179" s="2" t="n">
         <v>0.2654148374514973</v>
       </c>
+      <c r="R179" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12199,11 +12739,14 @@
       <c r="Q180" s="2" t="n">
         <v>0.2960217145088007</v>
       </c>
+      <c r="R180" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12263,6 +12806,9 @@
       </c>
       <c r="Q181" s="2" t="n">
         <v>0.3448523606159767</v>
+      </c>
+      <c r="R181" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -12276,10 +12822,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P61"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -12289,12 +12835,13 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12378,11 +12925,16 @@
           <t>shapiro_p</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>zero_variance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -12419,7 +12971,7 @@
         <v>0.670341064576195</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.9557427093639976</v>
+        <v>0.9557427093639974</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0.77</v>
@@ -12438,11 +12990,14 @@
       <c r="P2" s="2" t="n">
         <v>0.6066559834840692</v>
       </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12479,7 +13034,7 @@
         <v>0.3622351249040958</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.9914503458918176</v>
+        <v>0.991450345891817</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0.95</v>
@@ -12498,11 +13053,14 @@
       <c r="P3" s="2" t="n">
         <v>0.06837283419133207</v>
       </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12539,7 +13097,7 @@
         <v>0.5665938328543403</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.9891421962214855</v>
+        <v>0.9891421962214857</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0.9399999999999999</v>
@@ -12558,11 +13116,14 @@
       <c r="P4" s="2" t="n">
         <v>0.1453173864624776</v>
       </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -12599,7 +13160,7 @@
         <v>1.553898323572039</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.9659027317900564</v>
+        <v>0.965902731790056</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0.82</v>
@@ -12618,11 +13179,14 @@
       <c r="P5" s="2" t="n">
         <v>0.03770851477487872</v>
       </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -12678,11 +13242,14 @@
       <c r="P6" s="2" t="n">
         <v>0.9344799151719897</v>
       </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -12719,7 +13286,7 @@
         <v>2.4902208737379</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.9956909853239987</v>
+        <v>0.9956909853239994</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0.98</v>
@@ -12738,11 +13305,14 @@
       <c r="P7" s="2" t="n">
         <v>0.8978835708275923</v>
       </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -12779,7 +13349,7 @@
         <v>5.083699440368207</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.03325298379404815</v>
+        <v>0.03325298379404935</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>-0.6899999999999999</v>
@@ -12798,11 +13368,14 @@
       <c r="P8" s="2" t="n">
         <v>0.003134178032610979</v>
       </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -12858,11 +13431,14 @@
       <c r="P9" s="2" t="n">
         <v>0.7377237809090718</v>
       </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -12918,11 +13494,14 @@
       <c r="P10" s="2" t="n">
         <v>0.07104920593223947</v>
       </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -12959,7 +13538,7 @@
         <v>4.096493273869385</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.9250822778810451</v>
+        <v>0.9250822778810444</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0.63</v>
@@ -12978,11 +13557,14 @@
       <c r="P11" s="2" t="n">
         <v>0.06072001398646486</v>
       </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -13019,7 +13601,7 @@
         <v>3.167639950679821</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.9960634776597982</v>
+        <v>0.9960634776597987</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0.98</v>
@@ -13038,11 +13620,14 @@
       <c r="P12" s="2" t="n">
         <v>0.5092797650313861</v>
       </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -13079,7 +13664,7 @@
         <v>7.249016682084734</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.9788328288598932</v>
+        <v>0.9788328288598944</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0.88</v>
@@ -13098,11 +13683,14 @@
       <c r="P13" s="2" t="n">
         <v>0.139701039506624</v>
       </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -13139,7 +13727,7 @@
         <v>2.108316864230806</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.9025843417909745</v>
+        <v>0.9025843417909749</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0.46</v>
@@ -13158,11 +13746,14 @@
       <c r="P14" s="2" t="n">
         <v>0.3743179132061978</v>
       </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -13218,11 +13809,14 @@
       <c r="P15" s="2" t="n">
         <v>0.1949352610791055</v>
       </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -13278,11 +13872,14 @@
       <c r="P16" s="2" t="n">
         <v>0.05311693155940984</v>
       </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -13319,7 +13916,7 @@
         <v>0.9227314524461208</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.9608806417939895</v>
+        <v>0.9608806417939889</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0.75</v>
@@ -13338,11 +13935,14 @@
       <c r="P17" s="2" t="n">
         <v>0.6986572363815217</v>
       </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -13379,7 +13979,7 @@
         <v>3.787272545425445</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.924665435687092</v>
+        <v>0.9246654356870913</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0.5600000000000001</v>
@@ -13398,11 +13998,14 @@
       <c r="P18" s="2" t="n">
         <v>0.819264904912584</v>
       </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -13458,11 +14061,14 @@
       <c r="P19" s="2" t="n">
         <v>0.9251912860368419</v>
       </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -13513,16 +14119,19 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q20" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -13573,16 +14182,19 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q21" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -13633,16 +14245,19 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q22" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -13693,16 +14308,19 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q23" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -13753,16 +14371,19 @@
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q24" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -13813,16 +14434,19 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P25" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q25" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -13878,11 +14502,14 @@
       <c r="P26" s="2" t="n">
         <v>0.6161845596195361</v>
       </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13938,11 +14565,14 @@
       <c r="P27" s="2" t="n">
         <v>0.5525825999542388</v>
       </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -13998,11 +14628,14 @@
       <c r="P28" s="2" t="n">
         <v>0.5811520966054884</v>
       </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -14058,11 +14691,14 @@
       <c r="P29" s="2" t="n">
         <v>0.6182481999270998</v>
       </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -14118,11 +14754,14 @@
       <c r="P30" s="2" t="n">
         <v>0.4225663272529863</v>
       </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -14178,11 +14817,14 @@
       <c r="P31" s="2" t="n">
         <v>0.8150144174525058</v>
       </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14238,11 +14880,14 @@
       <c r="P32" s="2" t="n">
         <v>0.6347652185474261</v>
       </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14298,11 +14943,14 @@
       <c r="P33" s="2" t="n">
         <v>0.9267958724540946</v>
       </c>
+      <c r="Q33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -14358,11 +15006,14 @@
       <c r="P34" s="2" t="n">
         <v>0.3151598554160618</v>
       </c>
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -14418,11 +15069,14 @@
       <c r="P35" s="2" t="n">
         <v>0.09421926461193673</v>
       </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -14478,11 +15132,14 @@
       <c r="P36" s="2" t="n">
         <v>0.6332939495329125</v>
       </c>
+      <c r="Q36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -14538,11 +15195,14 @@
       <c r="P37" s="2" t="n">
         <v>0.2770955094516919</v>
       </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -14598,11 +15258,14 @@
       <c r="P38" s="2" t="n">
         <v>0.1148982664301885</v>
       </c>
+      <c r="Q38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -14658,11 +15321,14 @@
       <c r="P39" s="2" t="n">
         <v>0.5531536410058751</v>
       </c>
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -14718,11 +15384,14 @@
       <c r="P40" s="2" t="n">
         <v>0.8476103233718499</v>
       </c>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -14778,11 +15447,14 @@
       <c r="P41" s="2" t="n">
         <v>0.9964476481978725</v>
       </c>
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -14838,11 +15510,14 @@
       <c r="P42" s="2" t="n">
         <v>0.03133824557650202</v>
       </c>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -14898,11 +15573,14 @@
       <c r="P43" s="2" t="n">
         <v>0.5771551852591277</v>
       </c>
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -14958,11 +15636,14 @@
       <c r="P44" s="2" t="n">
         <v>0.1693401166783458</v>
       </c>
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -15018,11 +15699,14 @@
       <c r="P45" s="2" t="n">
         <v>0.4035743982891202</v>
       </c>
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -15078,11 +15762,14 @@
       <c r="P46" s="2" t="n">
         <v>0.8992432955202595</v>
       </c>
+      <c r="Q46" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -15138,11 +15825,14 @@
       <c r="P47" s="2" t="n">
         <v>0.997683209821168</v>
       </c>
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -15198,11 +15888,14 @@
       <c r="P48" s="2" t="n">
         <v>0.9316958267708093</v>
       </c>
+      <c r="Q48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -15258,11 +15951,14 @@
       <c r="P49" s="2" t="n">
         <v>0.5792774943787402</v>
       </c>
+      <c r="Q49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -15313,16 +16009,19 @@
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q50" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -15373,16 +16072,19 @@
         </is>
       </c>
       <c r="O51" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P51" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q51" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -15433,16 +16135,19 @@
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q52" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -15493,16 +16198,19 @@
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P53" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q53" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -15553,16 +16261,19 @@
         </is>
       </c>
       <c r="O54" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q54" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -15613,16 +16324,19 @@
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P55" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q55" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -15678,11 +16392,14 @@
       <c r="P56" s="2" t="n">
         <v>0.569859010648643</v>
       </c>
+      <c r="Q56" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -15738,11 +16455,14 @@
       <c r="P57" s="2" t="n">
         <v>0.9658142936434274</v>
       </c>
+      <c r="Q57" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -15798,11 +16518,14 @@
       <c r="P58" s="2" t="n">
         <v>0.4518590721308333</v>
       </c>
+      <c r="Q58" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -15858,11 +16581,14 @@
       <c r="P59" s="2" t="n">
         <v>0.6975140379699104</v>
       </c>
+      <c r="Q59" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -15918,11 +16644,14 @@
       <c r="P60" s="2" t="n">
         <v>0.954595674927508</v>
       </c>
+      <c r="Q60" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -15977,6 +16706,9 @@
       </c>
       <c r="P61" s="2" t="n">
         <v>0.04925616193621895</v>
+      </c>
+      <c r="Q61" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -15993,7 +16725,7 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
@@ -16030,7 +16762,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -16051,7 +16783,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -16072,7 +16804,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -16093,7 +16825,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -16114,7 +16846,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -16135,7 +16867,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -16156,7 +16888,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -16177,7 +16909,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -16198,7 +16930,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -16219,7 +16951,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -16240,7 +16972,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -16261,7 +16993,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -16282,7 +17014,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -16303,7 +17035,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -16324,7 +17056,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -16345,7 +17077,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -16366,7 +17098,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -16387,7 +17119,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -16408,7 +17140,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -16429,7 +17161,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -16461,7 +17193,7 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
@@ -16498,7 +17230,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -16519,7 +17251,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -16540,7 +17272,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -16561,7 +17293,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -16582,7 +17314,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -16603,7 +17335,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -16624,7 +17356,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -16645,7 +17377,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -16666,7 +17398,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -16687,7 +17419,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -16708,7 +17440,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -16729,7 +17461,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -16750,7 +17482,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -16771,7 +17503,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -16792,7 +17524,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -16813,7 +17545,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -16834,7 +17566,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -16855,7 +17587,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -16876,7 +17608,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -16897,7 +17629,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -16929,7 +17661,7 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
@@ -16966,7 +17698,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -16987,7 +17719,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -17008,7 +17740,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -17029,7 +17761,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -17050,7 +17782,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -17071,7 +17803,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -17092,7 +17824,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -17113,7 +17845,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -17134,7 +17866,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -17155,7 +17887,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -17176,7 +17908,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -17197,7 +17929,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -17218,7 +17950,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -17239,7 +17971,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -17260,7 +17992,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -17281,7 +18013,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -17302,7 +18034,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -17323,7 +18055,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -17344,7 +18076,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -17365,7 +18097,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -17394,19 +18126,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17460,11 +18193,16 @@
           <t>rmsd_deg</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>zero_variance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -17483,7 +18221,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9557427093639976</v>
+        <v>0.9557427093639974</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.77</v>
@@ -17502,11 +18240,14 @@
       <c r="J2" s="2" t="n">
         <v>0.670341064576195</v>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -17525,7 +18266,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9914503458918176</v>
+        <v>0.991450345891817</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.95</v>
@@ -17544,11 +18285,14 @@
       <c r="J3" s="2" t="n">
         <v>0.3622351249040958</v>
       </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -17567,7 +18311,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9891421962214855</v>
+        <v>0.9891421962214857</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0.9399999999999999</v>
@@ -17586,11 +18330,14 @@
       <c r="J4" s="2" t="n">
         <v>0.5665938328543403</v>
       </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -17609,7 +18356,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9659027317900564</v>
+        <v>0.965902731790056</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.82</v>
@@ -17628,11 +18375,14 @@
       <c r="J5" s="2" t="n">
         <v>1.553898323572039</v>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -17670,11 +18420,14 @@
       <c r="J6" s="2" t="n">
         <v>0.9754852272440755</v>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -17693,7 +18446,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9956909853239987</v>
+        <v>0.9956909853239994</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0.98</v>
@@ -17712,11 +18465,14 @@
       <c r="J7" s="2" t="n">
         <v>2.4902208737379</v>
       </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -17735,7 +18491,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.03325298379404815</v>
+        <v>0.03325298379404935</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>-0.6899999999999999</v>
@@ -17754,11 +18510,14 @@
       <c r="J8" s="2" t="n">
         <v>5.083699440368207</v>
       </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -17796,11 +18555,14 @@
       <c r="J9" s="2" t="n">
         <v>0.4270496792779837</v>
       </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -17838,11 +18600,14 @@
       <c r="J10" s="2" t="n">
         <v>5.294045172239675</v>
       </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -17861,7 +18626,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.9250822778810451</v>
+        <v>0.9250822778810444</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0.63</v>
@@ -17880,11 +18645,14 @@
       <c r="J11" s="2" t="n">
         <v>4.096493273869385</v>
       </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -17903,7 +18671,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.9960634776597982</v>
+        <v>0.9960634776597987</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0.98</v>
@@ -17922,11 +18690,14 @@
       <c r="J12" s="2" t="n">
         <v>3.167639950679821</v>
       </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -17945,7 +18716,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9788328288598932</v>
+        <v>0.9788328288598944</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0.88</v>
@@ -17964,11 +18735,14 @@
       <c r="J13" s="2" t="n">
         <v>7.249016682084734</v>
       </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -17987,7 +18761,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9025843417909745</v>
+        <v>0.9025843417909749</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0.46</v>
@@ -18006,11 +18780,14 @@
       <c r="J14" s="2" t="n">
         <v>2.108316864230806</v>
       </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -18048,11 +18825,14 @@
       <c r="J15" s="2" t="n">
         <v>3.662813126546316</v>
       </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -18090,11 +18870,14 @@
       <c r="J16" s="2" t="n">
         <v>2.097264090825634</v>
       </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -18113,7 +18896,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.9608806417939895</v>
+        <v>0.9608806417939889</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0.75</v>
@@ -18132,11 +18915,14 @@
       <c r="J17" s="2" t="n">
         <v>0.9227314524461208</v>
       </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -18155,7 +18941,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.924665435687092</v>
+        <v>0.9246654356870913</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0.5600000000000001</v>
@@ -18174,11 +18960,14 @@
       <c r="J18" s="2" t="n">
         <v>3.787272545425445</v>
       </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -18216,11 +19005,14 @@
       <c r="J19" s="2" t="n">
         <v>3.423239206755304</v>
       </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -18258,11 +19050,14 @@
       <c r="J20" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -18299,12 +19094,15 @@
       </c>
       <c r="J21" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -18342,11 +19140,14 @@
       <c r="J22" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -18383,12 +19184,15 @@
       </c>
       <c r="J23" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -18426,11 +19230,14 @@
       <c r="J24" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -18467,12 +19274,15 @@
       </c>
       <c r="J25" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -18510,11 +19320,14 @@
       <c r="J26" s="2" t="n">
         <v>0.3530049574722713</v>
       </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -18552,11 +19365,14 @@
       <c r="J27" s="2" t="n">
         <v>0.3664866982579307</v>
       </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -18594,11 +19410,14 @@
       <c r="J28" s="2" t="n">
         <v>0.3274904578762554</v>
       </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -18636,11 +19455,14 @@
       <c r="J29" s="2" t="n">
         <v>1.031691572128029</v>
       </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -18678,11 +19500,14 @@
       <c r="J30" s="2" t="n">
         <v>1.806526362940769</v>
       </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -18720,11 +19545,14 @@
       <c r="J31" s="2" t="n">
         <v>2.12958622741602</v>
       </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -18762,11 +19590,14 @@
       <c r="J32" s="2" t="n">
         <v>3.275316778572719</v>
       </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -18804,11 +19635,14 @@
       <c r="J33" s="2" t="n">
         <v>3.631811826465841</v>
       </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -18846,11 +19680,14 @@
       <c r="J34" s="2" t="n">
         <v>6.892236833672249</v>
       </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -18888,11 +19725,14 @@
       <c r="J35" s="2" t="n">
         <v>2.638164946646492</v>
       </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -18930,11 +19770,14 @@
       <c r="J36" s="2" t="n">
         <v>1.46735427604535</v>
       </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -18972,11 +19815,14 @@
       <c r="J37" s="2" t="n">
         <v>3.874414241441638</v>
       </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -19014,11 +19860,14 @@
       <c r="J38" s="2" t="n">
         <v>1.087920690386686</v>
       </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -19056,11 +19905,14 @@
       <c r="J39" s="2" t="n">
         <v>0.8301032638000096</v>
       </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -19098,11 +19950,14 @@
       <c r="J40" s="2" t="n">
         <v>1.020616060454243</v>
       </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -19140,11 +19995,14 @@
       <c r="J41" s="2" t="n">
         <v>3.433113955080935</v>
       </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -19182,11 +20040,14 @@
       <c r="J42" s="2" t="n">
         <v>5.101004102835328</v>
       </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -19224,11 +20085,14 @@
       <c r="J43" s="2" t="n">
         <v>8.497756846872674</v>
       </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19266,11 +20130,14 @@
       <c r="J44" s="2" t="n">
         <v>5.164634546606368</v>
       </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19308,11 +20175,14 @@
       <c r="J45" s="2" t="n">
         <v>7.774060500579262</v>
       </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -19350,11 +20220,14 @@
       <c r="J46" s="2" t="n">
         <v>3.270682905245734</v>
       </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -19392,11 +20265,14 @@
       <c r="J47" s="2" t="n">
         <v>4.867644878857395</v>
       </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -19434,11 +20310,14 @@
       <c r="J48" s="2" t="n">
         <v>1.95179404651208</v>
       </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -19476,11 +20355,14 @@
       <c r="J49" s="2" t="n">
         <v>3.526591839155758</v>
       </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -19518,11 +20400,14 @@
       <c r="J50" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -19559,12 +20444,15 @@
       </c>
       <c r="J51" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -19602,11 +20490,14 @@
       <c r="J52" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -19643,12 +20534,15 @@
       </c>
       <c r="J53" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -19686,11 +20580,14 @@
       <c r="J54" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -19727,12 +20624,15 @@
       </c>
       <c r="J55" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -19770,11 +20670,14 @@
       <c r="J56" s="2" t="n">
         <v>0.8791473141629899</v>
       </c>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -19812,11 +20715,14 @@
       <c r="J57" s="2" t="n">
         <v>0.5341582162618113</v>
       </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -19854,11 +20760,14 @@
       <c r="J58" s="2" t="n">
         <v>1.357387196049822</v>
       </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -19896,11 +20805,14 @@
       <c r="J59" s="2" t="n">
         <v>4.338548144252868</v>
       </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -19938,11 +20850,14 @@
       <c r="J60" s="2" t="n">
         <v>4.499286054475755</v>
       </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -19979,6 +20894,9 @@
       </c>
       <c r="J61" s="2" t="n">
         <v>8.726158948815911</v>
+      </c>
+      <c r="K61" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -19992,10 +20910,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P61"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -20011,6 +20929,7 @@
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20094,11 +21013,16 @@
           <t>shapiro_p</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>zero_variance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -20135,7 +21059,7 @@
         <v>3.172743292483649</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.9552063929370925</v>
+        <v>0.9552063929370916</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0.76</v>
@@ -20154,11 +21078,14 @@
       <c r="P2" s="2" t="n">
         <v>0.6025690140221178</v>
       </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -20195,7 +21122,7 @@
         <v>2.857961311344654</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.9912871699981776</v>
+        <v>0.9912871699981768</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0.95</v>
@@ -20214,11 +21141,14 @@
       <c r="P3" s="2" t="n">
         <v>0.07411295680054605</v>
       </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -20255,7 +21185,7 @@
         <v>0.5665938328543403</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.9891421962214855</v>
+        <v>0.9891421962214857</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0.9399999999999999</v>
@@ -20274,11 +21204,14 @@
       <c r="P4" s="2" t="n">
         <v>0.1453173864624776</v>
       </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -20334,11 +21267,14 @@
       <c r="P5" s="2" t="n">
         <v>0.03770851477486138</v>
       </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -20375,7 +21311,7 @@
         <v>1.739507319411368</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.9955375394541043</v>
+        <v>0.9955375394541045</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0.97</v>
@@ -20394,11 +21330,14 @@
       <c r="P6" s="2" t="n">
         <v>0.9446465575543979</v>
       </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -20435,7 +21374,7 @@
         <v>2.4902208737379</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.9956909853239987</v>
+        <v>0.9956909853239994</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0.98</v>
@@ -20454,11 +21393,14 @@
       <c r="P7" s="2" t="n">
         <v>0.8978835708275923</v>
       </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -20514,11 +21456,14 @@
       <c r="P8" s="2" t="n">
         <v>0.002854143560296695</v>
       </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -20574,11 +21519,14 @@
       <c r="P9" s="2" t="n">
         <v>0.5369424262226286</v>
       </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -20634,11 +21582,14 @@
       <c r="P10" s="2" t="n">
         <v>0.05683840328853819</v>
       </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -20694,11 +21645,14 @@
       <c r="P11" s="2" t="n">
         <v>0.08716074134650839</v>
       </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -20735,7 +21689,7 @@
         <v>3.071860766934038</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.9969711589644978</v>
+        <v>0.9969711589644982</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0.98</v>
@@ -20754,11 +21708,14 @@
       <c r="P12" s="2" t="n">
         <v>0.6028336031785568</v>
       </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -20795,7 +21752,7 @@
         <v>6.957808563046269</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.9794607013928694</v>
+        <v>0.9794607013928687</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0.89</v>
@@ -20814,11 +21771,14 @@
       <c r="P13" s="2" t="n">
         <v>0.2339437038676491</v>
       </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -20855,7 +21815,7 @@
         <v>2.108316864230806</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.9025843417909745</v>
+        <v>0.9025843417909749</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0.46</v>
@@ -20874,11 +21834,14 @@
       <c r="P14" s="2" t="n">
         <v>0.3743179132061978</v>
       </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -20934,11 +21897,14 @@
       <c r="P15" s="2" t="n">
         <v>0.1949352610791055</v>
       </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -20994,11 +21960,14 @@
       <c r="P16" s="2" t="n">
         <v>0.05311693155940984</v>
       </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -21035,7 +22004,7 @@
         <v>0.9227314524461208</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.9608806417939895</v>
+        <v>0.9608806417939889</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0.75</v>
@@ -21054,11 +22023,14 @@
       <c r="P17" s="2" t="n">
         <v>0.6986572363815217</v>
       </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -21095,7 +22067,7 @@
         <v>3.787272545425445</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.924665435687092</v>
+        <v>0.9246654356870913</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0.5600000000000001</v>
@@ -21114,11 +22086,14 @@
       <c r="P18" s="2" t="n">
         <v>0.819264904912584</v>
       </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -21174,11 +22149,14 @@
       <c r="P19" s="2" t="n">
         <v>0.9251912860368419</v>
       </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -21229,16 +22207,19 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q20" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -21289,16 +22270,19 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q21" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -21349,16 +22333,19 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q22" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -21409,16 +22396,19 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q23" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -21469,16 +22459,19 @@
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q24" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -21529,16 +22522,19 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P25" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q25" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -21594,11 +22590,14 @@
       <c r="P26" s="2" t="n">
         <v>0.6161845596195361</v>
       </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -21654,11 +22653,14 @@
       <c r="P27" s="2" t="n">
         <v>0.5525825999542388</v>
       </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -21714,11 +22716,14 @@
       <c r="P28" s="2" t="n">
         <v>0.5811520966054884</v>
       </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -21774,11 +22779,14 @@
       <c r="P29" s="2" t="n">
         <v>0.9121334413508366</v>
       </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -21834,11 +22842,14 @@
       <c r="P30" s="2" t="n">
         <v>0.5886624210907011</v>
       </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -21894,11 +22905,14 @@
       <c r="P31" s="2" t="n">
         <v>0.913660426593678</v>
       </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -21954,11 +22968,14 @@
       <c r="P32" s="2" t="n">
         <v>0.6347652185475476</v>
       </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -22014,11 +23031,14 @@
       <c r="P33" s="2" t="n">
         <v>0.92753147600468</v>
       </c>
+      <c r="Q33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -22074,11 +23094,14 @@
       <c r="P34" s="2" t="n">
         <v>0.3151598554160618</v>
       </c>
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -22134,11 +23157,14 @@
       <c r="P35" s="2" t="n">
         <v>0.08870334765663412</v>
       </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -22194,11 +23220,14 @@
       <c r="P36" s="2" t="n">
         <v>0.6332939495329125</v>
       </c>
+      <c r="Q36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -22254,11 +23283,14 @@
       <c r="P37" s="2" t="n">
         <v>0.2770955094516919</v>
       </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -22314,11 +23346,14 @@
       <c r="P38" s="2" t="n">
         <v>0.1230940643954077</v>
       </c>
+      <c r="Q38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -22374,11 +23409,14 @@
       <c r="P39" s="2" t="n">
         <v>0.5241403483362215</v>
       </c>
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -22434,11 +23472,14 @@
       <c r="P40" s="2" t="n">
         <v>0.8088512838241535</v>
       </c>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -22494,11 +23535,14 @@
       <c r="P41" s="2" t="n">
         <v>0.9974360313572285</v>
       </c>
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -22554,11 +23598,14 @@
       <c r="P42" s="2" t="n">
         <v>0.02969756896798373</v>
       </c>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -22614,11 +23661,14 @@
       <c r="P43" s="2" t="n">
         <v>0.5345202919959304</v>
       </c>
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -22674,11 +23724,14 @@
       <c r="P44" s="2" t="n">
         <v>0.1693401166783458</v>
       </c>
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -22734,11 +23787,14 @@
       <c r="P45" s="2" t="n">
         <v>0.4035743982891202</v>
       </c>
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -22794,11 +23850,14 @@
       <c r="P46" s="2" t="n">
         <v>0.8992432955202595</v>
       </c>
+      <c r="Q46" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -22854,11 +23913,14 @@
       <c r="P47" s="2" t="n">
         <v>0.997683209821168</v>
       </c>
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -22914,11 +23976,14 @@
       <c r="P48" s="2" t="n">
         <v>0.9316958267708093</v>
       </c>
+      <c r="Q48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -22974,11 +24039,14 @@
       <c r="P49" s="2" t="n">
         <v>0.5792774943787402</v>
       </c>
+      <c r="Q49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -23029,16 +24097,19 @@
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q50" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -23089,16 +24160,19 @@
         </is>
       </c>
       <c r="O51" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P51" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q51" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -23149,16 +24223,19 @@
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q52" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23209,16 +24286,19 @@
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P53" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q53" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23269,16 +24349,19 @@
         </is>
       </c>
       <c r="O54" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q54" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -23329,16 +24412,19 @@
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>1</v>
+        <v/>
       </c>
       <c r="P55" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Q55" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -23394,11 +24480,14 @@
       <c r="P56" s="2" t="n">
         <v>0.569859010648643</v>
       </c>
+      <c r="Q56" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -23454,11 +24543,14 @@
       <c r="P57" s="2" t="n">
         <v>0.9658142936434274</v>
       </c>
+      <c r="Q57" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -23514,11 +24606,14 @@
       <c r="P58" s="2" t="n">
         <v>0.4518590721308333</v>
       </c>
+      <c r="Q58" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -23574,11 +24669,14 @@
       <c r="P59" s="2" t="n">
         <v>0.3718395984258244</v>
       </c>
+      <c r="Q59" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -23634,11 +24732,14 @@
       <c r="P60" s="2" t="n">
         <v>0.6529823663386057</v>
       </c>
+      <c r="Q60" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -23693,6 +24794,9 @@
       </c>
       <c r="P61" s="2" t="n">
         <v>0.08312948511705628</v>
+      </c>
+      <c r="Q61" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23706,10 +24810,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -23719,6 +24823,7 @@
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23772,11 +24877,16 @@
           <t>rmsd_deg</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>zero_variance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -23795,7 +24905,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9552063929370925</v>
+        <v>0.9552063929370916</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.76</v>
@@ -23814,11 +24924,14 @@
       <c r="J2" s="2" t="n">
         <v>3.172743292483649</v>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -23837,7 +24950,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9912871699981776</v>
+        <v>0.9912871699981768</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.95</v>
@@ -23856,11 +24969,14 @@
       <c r="J3" s="2" t="n">
         <v>2.857961311344654</v>
       </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -23879,7 +24995,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9891421962214855</v>
+        <v>0.9891421962214857</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0.9399999999999999</v>
@@ -23898,11 +25014,14 @@
       <c r="J4" s="2" t="n">
         <v>0.5665938328543403</v>
       </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -23940,11 +25059,14 @@
       <c r="J5" s="2" t="n">
         <v>4.206044969530678</v>
       </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -23963,7 +25085,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9955375394541043</v>
+        <v>0.9955375394541045</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0.97</v>
@@ -23982,11 +25104,14 @@
       <c r="J6" s="2" t="n">
         <v>1.739507319411368</v>
       </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -24005,7 +25130,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9956909853239987</v>
+        <v>0.9956909853239994</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0.98</v>
@@ -24024,11 +25149,14 @@
       <c r="J7" s="2" t="n">
         <v>2.4902208737379</v>
       </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -24066,11 +25194,14 @@
       <c r="J8" s="2" t="n">
         <v>5.028123762540911</v>
       </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -24108,11 +25239,14 @@
       <c r="J9" s="2" t="n">
         <v>0.369304365375925</v>
       </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -24150,11 +25284,14 @@
       <c r="J10" s="2" t="n">
         <v>5.08660846874277</v>
       </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -24192,11 +25329,14 @@
       <c r="J11" s="2" t="n">
         <v>3.900009157498403</v>
       </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -24215,7 +25355,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.9969711589644978</v>
+        <v>0.9969711589644982</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0.98</v>
@@ -24234,11 +25374,14 @@
       <c r="J12" s="2" t="n">
         <v>3.071860766934038</v>
       </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -24257,7 +25400,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.9794607013928694</v>
+        <v>0.9794607013928687</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0.89</v>
@@ -24276,11 +25419,14 @@
       <c r="J13" s="2" t="n">
         <v>6.957808563046269</v>
       </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -24299,7 +25445,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9025843417909745</v>
+        <v>0.9025843417909749</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0.46</v>
@@ -24318,11 +25464,14 @@
       <c r="J14" s="2" t="n">
         <v>2.108316864230806</v>
       </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -24360,11 +25509,14 @@
       <c r="J15" s="2" t="n">
         <v>3.662813126546316</v>
       </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -24402,11 +25554,14 @@
       <c r="J16" s="2" t="n">
         <v>2.097264090825634</v>
       </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -24425,7 +25580,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.9608806417939895</v>
+        <v>0.9608806417939889</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0.75</v>
@@ -24444,11 +25599,14 @@
       <c r="J17" s="2" t="n">
         <v>0.9227314524461208</v>
       </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -24467,7 +25625,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.924665435687092</v>
+        <v>0.9246654356870913</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0.5600000000000001</v>
@@ -24486,11 +25644,14 @@
       <c r="J18" s="2" t="n">
         <v>3.787272545425445</v>
       </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -24528,11 +25689,14 @@
       <c r="J19" s="2" t="n">
         <v>3.423239206755304</v>
       </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -24570,11 +25734,14 @@
       <c r="J20" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -24611,12 +25778,15 @@
       </c>
       <c r="J21" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -24654,11 +25824,14 @@
       <c r="J22" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -24695,12 +25868,15 @@
       </c>
       <c r="J23" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -24738,11 +25914,14 @@
       <c r="J24" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -24779,12 +25958,15 @@
       </c>
       <c r="J25" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -24822,11 +26004,14 @@
       <c r="J26" s="2" t="n">
         <v>0.3530049574722713</v>
       </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -24864,11 +26049,14 @@
       <c r="J27" s="2" t="n">
         <v>0.3664866982579307</v>
       </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -24906,11 +26094,14 @@
       <c r="J28" s="2" t="n">
         <v>0.3274904578762554</v>
       </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -24948,11 +26139,14 @@
       <c r="J29" s="2" t="n">
         <v>0.9662880005464217</v>
       </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -24990,11 +26184,14 @@
       <c r="J30" s="2" t="n">
         <v>1.764050736231813</v>
       </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -25032,11 +26229,14 @@
       <c r="J31" s="2" t="n">
         <v>1.973512097758714</v>
       </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -25074,11 +26274,14 @@
       <c r="J32" s="2" t="n">
         <v>0.6751507768110515</v>
       </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -25116,11 +26319,14 @@
       <c r="J33" s="2" t="n">
         <v>6.29577636197475</v>
       </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -25158,11 +26364,14 @@
       <c r="J34" s="2" t="n">
         <v>6.892236833672249</v>
       </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -25200,11 +26409,14 @@
       <c r="J35" s="2" t="n">
         <v>0.7545859791965377</v>
       </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -25242,11 +26454,14 @@
       <c r="J36" s="2" t="n">
         <v>3.975482001324765</v>
       </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -25284,11 +26499,14 @@
       <c r="J37" s="2" t="n">
         <v>3.874414241441638</v>
       </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -25326,11 +26544,14 @@
       <c r="J38" s="2" t="n">
         <v>1.223087428249866</v>
       </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -25368,11 +26589,14 @@
       <c r="J39" s="2" t="n">
         <v>0.7088924963833174</v>
       </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -25410,11 +26634,14 @@
       <c r="J40" s="2" t="n">
         <v>1.142591040448982</v>
       </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -25452,11 +26679,14 @@
       <c r="J41" s="2" t="n">
         <v>3.264263207174676</v>
       </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -25494,11 +26724,14 @@
       <c r="J42" s="2" t="n">
         <v>5.001242702711855</v>
       </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -25536,11 +26769,14 @@
       <c r="J43" s="2" t="n">
         <v>8.224971558787118</v>
       </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -25578,11 +26814,14 @@
       <c r="J44" s="2" t="n">
         <v>5.164634546606368</v>
       </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -25620,11 +26859,14 @@
       <c r="J45" s="2" t="n">
         <v>7.774060500579262</v>
       </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -25662,11 +26904,14 @@
       <c r="J46" s="2" t="n">
         <v>3.270682905245734</v>
       </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -25704,11 +26949,14 @@
       <c r="J47" s="2" t="n">
         <v>4.867644878857395</v>
       </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -25746,11 +26994,14 @@
       <c r="J48" s="2" t="n">
         <v>1.95179404651208</v>
       </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -25788,11 +27039,14 @@
       <c r="J49" s="2" t="n">
         <v>3.526591839155758</v>
       </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -25830,11 +27084,14 @@
       <c r="J50" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -25871,12 +27128,15 @@
       </c>
       <c r="J51" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -25914,11 +27174,14 @@
       <c r="J52" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -25955,12 +27218,15 @@
       </c>
       <c r="J53" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -25998,11 +27264,14 @@
       <c r="J54" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -26039,12 +27308,15 @@
       </c>
       <c r="J55" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -26082,11 +27354,14 @@
       <c r="J56" s="2" t="n">
         <v>0.8791473141629899</v>
       </c>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -26124,11 +27399,14 @@
       <c r="J57" s="2" t="n">
         <v>0.5341582162618113</v>
       </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -26166,11 +27444,14 @@
       <c r="J58" s="2" t="n">
         <v>1.357387196049822</v>
       </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -26208,11 +27489,14 @@
       <c r="J59" s="2" t="n">
         <v>3.555346326309155</v>
       </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26250,11 +27534,14 @@
       <c r="J60" s="2" t="n">
         <v>3.90464467013325</v>
       </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NOT_C7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26291,6 +27578,9 @@
       </c>
       <c r="J61" s="2" t="n">
         <v>7.297037069934618</v>
+      </c>
+      <c r="K61" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
